--- a/Lab1.xlsx
+++ b/Lab1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AgentSmith\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yacoo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA2EFF9-0ACC-4864-93B5-2CF77A23C5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BD127A-2B47-42A8-9911-F528D0EEA4ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="39096" windowHeight="13068" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="42">
   <si>
     <t>E1 Пиво</t>
   </si>
@@ -142,13 +142,10 @@
     <t>20. У сотрудника может быть только одна должность: менеджер по закупкам, менеджер по продажам, бухгалтер, руководитель.</t>
   </si>
   <si>
-    <t>21. Пивоварни, заведения, склада есть поле координаты</t>
-  </si>
-  <si>
-    <t>22. В исходящем платеже нужно отличать инициативную закупку, закупку под заказ и баланс запасов</t>
-  </si>
-  <si>
     <t>E15 Справочник адресов</t>
+  </si>
+  <si>
+    <t>21. В исходящем платеже нужно отличать инициативную закупку, закупку под заказ и баланс запасов</t>
   </si>
 </sst>
 </file>
@@ -639,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T43"/>
+  <dimension ref="A1:T42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36.5546875" customWidth="1"/>
@@ -1238,7 +1235,7 @@
     </row>
     <row r="21" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7" t="s">
@@ -1367,12 +1364,7 @@
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="A42" t="s">
         <v>41</v>
       </c>
     </row>
